--- a/mode_docx_gen/pmi_mtz/mtz1_modes/МТЗ 1 ст_7.xlsx
+++ b/mode_docx_gen/pmi_mtz/mtz1_modes/МТЗ 1 ст_7.xlsx
@@ -806,14 +806,14 @@
       <c r="AA2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
+      <c r="AB2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AC2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
+      <c r="AD2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AE2" s="2" t="n">
         <v>1</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>50</v>
@@ -1920,254 +1920,254 @@
           <t>0</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="BJ2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BK2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BL2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/mode_docx_gen/pmi_mtz/mtz1_modes/МТЗ 1 ст_7.xlsx
+++ b/mode_docx_gen/pmi_mtz/mtz1_modes/МТЗ 1 ст_7.xlsx
@@ -880,29 +880,6 @@
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1012,67 +989,67 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>40</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>40</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P2" s="2" t="n">
+      <c r="O2" t="n">
         <v>40</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="P2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="R2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2" t="n">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
         <v>40</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>5</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/mode_docx_gen/pmi_mtz/mtz1_modes/МТЗ 1 ст_7.xlsx
+++ b/mode_docx_gen/pmi_mtz/mtz1_modes/МТЗ 1 ст_7.xlsx
@@ -791,11 +791,11 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
+      <c r="W2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -803,17 +803,17 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="2" t="n">
-        <v>1</v>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
       </c>
       <c r="AE2" s="2" t="n">
         <v>1</v>
@@ -880,6 +880,29 @@
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -989,67 +1012,67 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>40</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>40</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="S2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1064,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1129,10 @@
     <col width="20" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1166,140 +1193,160 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>dIA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>IB</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dIB</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>IC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>IAB</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>dIC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>UAB_ptuv1</t>
+          <t>UA1</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>UBC_ptuv1</t>
+          <t>dUA1</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>UCA_ptuv1</t>
+          <t>UB1</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>U2_ptuv1</t>
+          <t>dUB1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>UAB_ptuv2</t>
+          <t>UC1</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>UBC_ptuv2</t>
+          <t>dUC1</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>UCA_ptuv2</t>
+          <t>UA2</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>U2_ptuv2</t>
+          <t>dUA2</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>UB2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dUB2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>UC2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dUC2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>KPONvnesh_ptuv1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>KPONvnesh_ptuv2</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>IA2harm</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>IB2harm</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>IC2harm</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>VNN1vkl</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>VNN2vkl</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>OV_lvrbvtr1</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>vnesh_bnn_srab_lvrbvtr1</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>OV_lvrbvtr2</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>vnesh_bnn_srab_lvrbvtr2</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>OVlot</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>OVlo</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>OVzapv</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>OVzavr</t>
         </is>
@@ -1339,78 +1386,78 @@
       <c r="K2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>2</v>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
+      <c r="N2" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>120</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>316</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>50</v>
+        <v>224</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>316</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>224</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AE2" s="2" t="n">
+      <c r="AI2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
@@ -1421,6 +1468,18 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1435,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:CG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1561,27 @@
     <col width="20" customWidth="1" min="62" max="62"/>
     <col width="20" customWidth="1" min="63" max="63"/>
     <col width="20" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="65" max="65"/>
+    <col width="20" customWidth="1" min="66" max="66"/>
+    <col width="20" customWidth="1" min="67" max="67"/>
+    <col width="20" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="69" max="69"/>
+    <col width="20" customWidth="1" min="70" max="70"/>
+    <col width="20" customWidth="1" min="71" max="71"/>
+    <col width="20" customWidth="1" min="72" max="72"/>
+    <col width="20" customWidth="1" min="73" max="73"/>
+    <col width="20" customWidth="1" min="74" max="74"/>
+    <col width="20" customWidth="1" min="75" max="75"/>
+    <col width="20" customWidth="1" min="76" max="76"/>
+    <col width="20" customWidth="1" min="77" max="77"/>
+    <col width="20" customWidth="1" min="78" max="78"/>
+    <col width="20" customWidth="1" min="79" max="79"/>
+    <col width="20" customWidth="1" min="80" max="80"/>
+    <col width="20" customWidth="1" min="81" max="81"/>
+    <col width="20" customWidth="1" min="82" max="82"/>
+    <col width="20" customWidth="1" min="83" max="83"/>
+    <col width="20" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1825,121 +1905,226 @@
           <t>pusk_lvalv</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dIAB</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dIBC</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dICA</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>I0</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>UAB_ptuv1</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>UBC_ptuv1</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>UCA_ptuv1</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>U2_ptuv1</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>U0_ptuv1</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>U1_ptuv1</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>UAB_ptuv2</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>UBC_ptuv2</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>UCA_ptuv2</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>U2_ptuv2</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>U0_ptuv2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>U1_ptuv2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -2052,14 +2237,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -2087,9 +2272,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="BB2" s="2" t="inlineStr">
@@ -2102,14 +2287,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BD2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="BF2" s="2" t="inlineStr">
@@ -2137,14 +2322,119 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BM2" s="2" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="BN2" s="2" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="BO2" s="2" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="BP2" s="2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="BQ2" s="2" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="BR2" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BU2" s="2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BV2" s="2" t="inlineStr">
+        <is>
+          <t>92.26</t>
+        </is>
+      </c>
+      <c r="BW2" s="2" t="inlineStr">
+        <is>
+          <t>60.42</t>
+        </is>
+      </c>
+      <c r="BX2" s="2" t="inlineStr">
+        <is>
+          <t>92.26</t>
+        </is>
+      </c>
+      <c r="BY2" s="2" t="inlineStr">
+        <is>
+          <t>11.62</t>
+        </is>
+      </c>
+      <c r="BZ2" s="2" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="CA2" s="2" t="inlineStr">
+        <is>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="CB2" s="2" t="inlineStr">
+        <is>
+          <t>92.26</t>
+        </is>
+      </c>
+      <c r="CC2" s="2" t="inlineStr">
+        <is>
+          <t>60.42</t>
+        </is>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
+        <is>
+          <t>92.26</t>
+        </is>
+      </c>
+      <c r="CE2" s="2" t="inlineStr">
+        <is>
+          <t>11.62</t>
+        </is>
+      </c>
+      <c r="CF2" s="2" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="CG2" s="2" t="inlineStr">
+        <is>
+          <t>46.5</t>
         </is>
       </c>
     </row>
